--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92571327573</v>
+        <v>46157.93108607955</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93108607955</v>
+        <v>46157.93178041692</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93178041692</v>
+        <v>46157.93402897284</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93402897284</v>
+        <v>46157.93720869446</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93720869446</v>
+        <v>46158.28218932862</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28218932862</v>
+        <v>46158.29693364143</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29693364143</v>
+        <v>46158.29818017843</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29818017843</v>
+        <v>46158.33389909378</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.33389909378</v>
+        <v>46158.36859753074</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.11_Комплект_Для_суда/Для суда от Виктории/Для СУДА/34. ЭК ВОСТОК/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36859753074</v>
+        <v>46158.37290349786</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
